--- a/markdown_generator/paper.xlsx
+++ b/markdown_generator/paper.xlsx
@@ -40,7 +40,7 @@
     <t>2021-11-07</t>
   </si>
   <si>
-    <t>PowerDet: Efficient and Lightweight Object Detection for Electric Power Open Scenes</t>
+    <t>PowerDet:Efficient and Lightweight Object Detection for Electric Power Open Scenes</t>
   </si>
   <si>
     <t>CCIS2021</t>

--- a/markdown_generator/paper.xlsx
+++ b/markdown_generator/paper.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>pub_date</t>
   </si>
@@ -43,7 +43,7 @@
     <t>PowerDet:Efficient and Lightweight Object Detection for Electric Power Open Scenes</t>
   </si>
   <si>
-    <t>CCIS2021</t>
+    <t>CCIS</t>
   </si>
   <si>
     <t>There are problems with the schemes in open electric power scenes, e.g., only able to detect single category, low detection accuracy of multi-scale objects, and difficulty in deploying models on mobile devices. To address the challenges mentioned above, we propose an object detection model, named PowerDet. It is able to detect 9 different types of power facilities efficiently with low cost.</t>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t>https://journals.sagepub.com/doi/pdf/10.1177/20406223221136071</t>
-  </si>
-  <si>
-    <t/>
   </si>
 </sst>
 </file>
@@ -99,7 +96,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,6 +114,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -148,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -162,19 +165,10 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -488,13 +482,13 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="11" width="18.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="10" width="11.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="11" width="48.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="11" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="11" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="11" width="18.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="18.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="11.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="48.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="12.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="8" width="18.719285714285714" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5" customFormat="1" s="1">
@@ -520,7 +514,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -530,7 +524,7 @@
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="4" t="s">
@@ -544,71 +538,59 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>25</v>
-      </c>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
